--- a/JsonConverter/ExcelFiles/BulletData.xlsx
+++ b/JsonConverter/ExcelFiles/BulletData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -58,13 +58,19 @@
     <t>Damage</t>
   </si>
   <si>
-    <t>BulletLevel</t>
+    <t>FireSpeed</t>
   </si>
   <si>
     <t>PrefabPath</t>
   </si>
   <si>
     <t>IconPath</t>
+  </si>
+  <si>
+    <t>UpgradeIngredientTableId</t>
+  </si>
+  <si>
+    <t>NextBulletId</t>
   </si>
   <si>
     <t>bullet_normalbullet_01</t>
@@ -79,6 +85,12 @@
     <t>Prefab/Bullet</t>
   </si>
   <si>
+    <t>bullet/bullet[bullets_3]</t>
+  </si>
+  <si>
+    <t>upgrade_normalbullet_01</t>
+  </si>
+  <si>
     <t>bullet_ironbullet_01</t>
   </si>
   <si>
@@ -86,6 +98,24 @@
   </si>
   <si>
     <t>좀 더 강한 강철 총알이다.</t>
+  </si>
+  <si>
+    <t>bullet/bullet[bullets_13]</t>
+  </si>
+  <si>
+    <t>upgrade_ironbullet_01</t>
+  </si>
+  <si>
+    <t>bullet_goldenbullet_01</t>
+  </si>
+  <si>
+    <t>황금 총알</t>
+  </si>
+  <si>
+    <t>황금으로 만든 매우 강한 총알이다.</t>
+  </si>
+  <si>
+    <t>bullet/bullet[bullets_0]</t>
   </si>
 </sst>
 </file>
@@ -160,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -173,17 +203,23 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,7 +445,11 @@
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" min="6" max="6" width="23.25"/>
-    <col customWidth="1" min="7" max="26" width="11.0"/>
+    <col customWidth="1" min="7" max="8" width="11.0"/>
+    <col customWidth="1" min="9" max="9" width="17.75"/>
+    <col customWidth="1" min="10" max="10" width="33.5"/>
+    <col customWidth="1" min="11" max="11" width="19.75"/>
+    <col customWidth="1" min="12" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -478,8 +518,12 @@
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -497,79 +541,89 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
+      <c r="J3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
-      <c r="D4" s="6">
-        <v>10.0</v>
+      <c r="D4" s="4">
+        <v>8.0</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>5.0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>50.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>1.0</v>
+      <c r="G4" s="4">
+        <v>4.0</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="I4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -588,30 +642,36 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>10.0</v>
       </c>
-      <c r="E5" s="6">
-        <v>5.0</v>
+      <c r="E5" s="4">
+        <v>6.0</v>
       </c>
       <c r="F5" s="3">
         <v>65.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>1.0</v>
+      <c r="G5" s="4">
+        <v>7.0</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="I5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -629,15 +689,31 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>80.0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10.0</v>
+      </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>

--- a/JsonConverter/ExcelFiles/BulletData.xlsx
+++ b/JsonConverter/ExcelFiles/BulletData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -100,22 +100,28 @@
     <t>좀 더 강한 강철 총알이다.</t>
   </si>
   <si>
+    <t>Prefab/Bullet_Iron</t>
+  </si>
+  <si>
     <t>bullet/bullet[bullets_13]</t>
   </si>
   <si>
     <t>upgrade_ironbullet_01</t>
   </si>
   <si>
-    <t>bullet_goldenbullet_01</t>
+    <t>bullet_plasmabullet_01</t>
   </si>
   <si>
-    <t>황금 총알</t>
+    <t>플라즈마 총알</t>
   </si>
   <si>
-    <t>황금으로 만든 매우 강한 총알이다.</t>
+    <t>플라즈마로 만들어진 매우 강한 총알이다.</t>
   </si>
   <si>
-    <t>bullet/bullet[bullets_0]</t>
+    <t>Prefab/Bullet_Plasma</t>
+  </si>
+  <si>
+    <t>bullet/bullet[bullets_2]</t>
   </si>
 </sst>
 </file>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -203,20 +209,17 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
@@ -445,7 +448,8 @@
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" min="6" max="6" width="23.25"/>
-    <col customWidth="1" min="7" max="8" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col customWidth="1" min="8" max="8" width="16.63"/>
     <col customWidth="1" min="9" max="9" width="17.75"/>
     <col customWidth="1" min="10" max="10" width="33.5"/>
     <col customWidth="1" min="11" max="11" width="19.75"/>
@@ -518,10 +522,10 @@
       <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="L2" s="3"/>
@@ -541,54 +545,54 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -600,28 +604,28 @@
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>8.0</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>5.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>50.0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>4.0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="3"/>
@@ -650,27 +654,29 @@
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>10.0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>6.0</v>
       </c>
       <c r="F5" s="3">
         <v>65.0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>7.0</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -689,30 +695,32 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="4">
+      <c r="C6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3">
         <v>14.0</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>6.0</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>80.0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>10.0</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="4" t="s">
-        <v>34</v>
+      <c r="H6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>

--- a/JsonConverter/ExcelFiles/BulletData.xlsx
+++ b/JsonConverter/ExcelFiles/BulletData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -123,6 +123,21 @@
   <si>
     <t>bullet/bullet[bullets_2]</t>
   </si>
+  <si>
+    <t>bullet_boss_01</t>
+  </si>
+  <si>
+    <t>보스 총알</t>
+  </si>
+  <si>
+    <t>보스용</t>
+  </si>
+  <si>
+    <t>Prefab/Bullet_Boss</t>
+  </si>
+  <si>
+    <t>bullet/bullet[bullets_21]</t>
+  </si>
 </sst>
 </file>
 
@@ -218,11 +233,11 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,7 +681,7 @@
       <c r="G5" s="3">
         <v>7.0</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -675,7 +690,7 @@
       <c r="J5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="L5" s="3"/>
@@ -695,13 +710,13 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="3">
@@ -716,10 +731,10 @@
       <c r="G6" s="3">
         <v>10.0</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="3"/>
@@ -741,15 +756,33 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>30.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
